--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -1294,8 +1294,8 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable1" cacheId="0" dataPosition="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" itemPrintTitles="1" mergeItem="1" createdVersion="3" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="B3:H9" firstHeaderRow="1" firstDataRow="3" firstDataCol="3"/>
   <pivotFields count="7">
-    <pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="55">
+    <pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="54">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -1350,11 +1350,10 @@
         <item x="51"/>
         <item x="52"/>
         <item x="53"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="Payment method" axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="8">
+    <pivotField name="Payment method" axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="7">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -1362,11 +1361,10 @@
         <item x="4"/>
         <item x="5"/>
         <item x="6"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="206">
+    <pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="205">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -1572,20 +1570,18 @@
         <item x="202"/>
         <item x="203"/>
         <item x="204"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField name="Tax rate" axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="4">
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField name="Tax rate" axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="3">
     <field x="0"/>
@@ -1622,8 +1618,8 @@
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Значения" updatedVersion="3" minRefreshableVersion="3" showCalcMbrs="0" useAutoFormatting="1" itemPrintTitles="1" mergeItem="1" createdVersion="3" indent="0" compact="0" compactData="0" gridDropZones="1">
   <location ref="B4:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="2"/>
   <pivotFields count="7">
-    <pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="55">
+    <pivotField name="Company" axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="54">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -1678,11 +1674,10 @@
         <item x="51"/>
         <item x="52"/>
         <item x="53"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="Payment method" axis="axisCol" compact="0" outline="0" showAll="0">
-      <items count="8">
+    <pivotField name="Payment method" axis="axisCol" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="7">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -1690,11 +1685,10 @@
         <item x="4"/>
         <item x="5"/>
         <item x="6"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0">
-      <items count="206">
+    <pivotField name="OrderNo" axis="axisRow" compact="0" outline="0" showAll="0" defaultSubtotal="0">
+      <items count="205">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
@@ -1900,13 +1894,12 @@
         <item x="202"/>
         <item x="203"/>
         <item x="204"/>
-        <item t="default"/>
       </items>
     </pivotField>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField compact="0" outline="0" showAll="0" defaultSubtotal="0"/>
   </pivotFields>
   <rowFields count="2">
     <field x="0"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -841,6 +841,45 @@
   </x:si>
   <x:si>
     <x:t>1860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Data</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.TaxRate}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Итог Sum Amount paid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Итог Sum Items total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum Amount paid</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum Items total</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Company}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PaymentMethod}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.OrderNo}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.PaymentMethod}} Итог</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{item.Company}} Итог</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Общий итог</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sum of Items total</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1114,7 +1153,7 @@
       <x:diagonal/>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="7">
+  <x:cellStyleXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
@@ -1128,6 +1167,30 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -7055,11 +7118,143 @@
     <x:col min="6" max="6" width="13.832031" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="4" ht="11.25" customHeight="1"/>
-    <x:row r="5" ht="25.5" customHeight="1"/>
-    <x:row r="8" ht="12" customHeight="1"/>
-    <x:row r="9" ht="12.75" customHeight="1"/>
+    <x:row r="3" spans="1:8">
+      <x:c r="B3" s="4"/>
+      <x:c r="C3" s="6"/>
+      <x:c r="D3" s="6"/>
+      <x:c r="E3" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="G3" s="6"/>
+      <x:c r="H3" s="7"/>
+    </x:row>
+    <x:row r="4" spans="1:8" ht="11.25" customHeight="1">
+      <x:c r="B4" s="9"/>
+      <x:c r="C4" s="8"/>
+      <x:c r="D4" s="8"/>
+      <x:c r="E4" s="11" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="F4" s="6"/>
+      <x:c r="G4" s="11" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="H4" s="40" t="s">
+        <x:v>276</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8" ht="25.5" customHeight="1">
+      <x:c r="B5" s="13" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="13" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="D5" s="13" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E5" s="13" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="F5" s="13" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="G5" s="9"/>
+      <x:c r="H5" s="41"/>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="B6" s="3" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C6" s="3" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D6" s="3" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="E6" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F6" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G6" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H6" s="3">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="B7" s="3"/>
+      <x:c r="C7" s="3" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="D7" s="3"/>
+      <x:c r="E7" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F7" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G7" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H7" s="3">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8" ht="12" customHeight="1">
+      <x:c r="B8" s="3" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C8" s="3"/>
+      <x:c r="D8" s="3"/>
+      <x:c r="E8" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F8" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G8" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H8" s="3">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8" ht="12.75" customHeight="1">
+      <x:c r="B9" s="3" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C9" s="3"/>
+      <x:c r="D9" s="3"/>
+      <x:c r="E9" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G9" s="3">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H9" s="3">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells count="7">
+    <x:mergeCell ref="E4:F4"/>
+    <x:mergeCell ref="G4:G5"/>
+    <x:mergeCell ref="H4:H5"/>
+    <x:mergeCell ref="B6:B7"/>
+    <x:mergeCell ref="C7:D7"/>
+    <x:mergeCell ref="B8:D8"/>
+    <x:mergeCell ref="B9:D9"/>
+  </x:mergeCells>
   <x:phoneticPr fontId="0" type="noConversion"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7084,8 +7279,73 @@
     <x:col min="5" max="5" width="11" style="0" bestFit="1" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="7" spans="1:5" ht="11.25" customHeight="1"/>
+    <x:row r="4" spans="1:5">
+      <x:c r="B4" s="4" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="C4" s="6"/>
+      <x:c r="D4" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="7"/>
+    </x:row>
+    <x:row r="5" spans="1:5">
+      <x:c r="B5" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="D5" s="4" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="E5" s="4" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:5">
+      <x:c r="B6" s="11" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="D6" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E6" s="11">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:5" ht="11.25" customHeight="1">
+      <x:c r="B7" s="11" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C7" s="11"/>
+      <x:c r="D7" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E7" s="11">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:5">
+      <x:c r="B8" s="11" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="C8" s="11"/>
+      <x:c r="D8" s="11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E8" s="11">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
+  <x:mergeCells count="2">
+    <x:mergeCell ref="B7:C7"/>
+    <x:mergeCell ref="B8:C8"/>
+  </x:mergeCells>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>

--- a/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
+++ b/XLibur.Tests/Resource/Other/PivotTableReferenceFiles/TwoPivotTablesWithSingleSource/output.xlsx
@@ -1668,7 +1668,7 @@
       </pivotArea>
     </format>
   </formats>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
@@ -1983,7 +1983,7 @@
       </pivotArea>
     </format>
   </formats>
-  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1"/>
+  <pivotTableStyleInfo showRowHeaders="1" showColHeaders="1" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition enableEdit="0" hideValuesRow="1"/>
